--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/WISCONSIN_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/WISCONSIN_2014.xlsx
@@ -2353,7 +2353,7 @@
         <v>114</v>
       </c>
       <c r="D111">
-        <v>0.009236752552261</v>
+        <v>0.009236752552261002</v>
       </c>
     </row>
     <row r="112">
@@ -4585,7 +4585,7 @@
         <v>12</v>
       </c>
       <c r="D235">
-        <v>0.000972289742343</v>
+        <v>0.0009722897423430002</v>
       </c>
     </row>
     <row r="236">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C245">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C254">
@@ -5359,7 +5359,7 @@
         <v>12</v>
       </c>
       <c r="D278">
-        <v>0.000972289742343</v>
+        <v>0.0009722897423430002</v>
       </c>
     </row>
     <row r="279">
@@ -6439,7 +6439,7 @@
         <v>12</v>
       </c>
       <c r="D338">
-        <v>0.000972289742343</v>
+        <v>0.0009722897423430002</v>
       </c>
     </row>
     <row r="339">
@@ -6529,7 +6529,7 @@
         <v>12</v>
       </c>
       <c r="D343">
-        <v>0.000972289742343</v>
+        <v>0.0009722897423430002</v>
       </c>
     </row>
     <row r="344">
@@ -6601,7 +6601,7 @@
         <v>12</v>
       </c>
       <c r="D347">
-        <v>0.000972289742343</v>
+        <v>0.0009722897423430002</v>
       </c>
     </row>
     <row r="348">
@@ -10687,7 +10687,7 @@
         <v>12</v>
       </c>
       <c r="D574">
-        <v>0.000972289742343</v>
+        <v>0.0009722897423430002</v>
       </c>
     </row>
     <row r="575">
@@ -10993,7 +10993,7 @@
         <v>12</v>
       </c>
       <c r="D591">
-        <v>0.000972289742343</v>
+        <v>0.0009722897423430002</v>
       </c>
     </row>
     <row r="592">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C605">
@@ -11659,7 +11659,7 @@
         <v>12</v>
       </c>
       <c r="D628">
-        <v>0.000972289742343</v>
+        <v>0.0009722897423430002</v>
       </c>
     </row>
     <row r="629">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C701">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C737">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C742">
@@ -15313,7 +15313,7 @@
         <v>12</v>
       </c>
       <c r="D831">
-        <v>0.000972289742343</v>
+        <v>0.0009722897423430002</v>
       </c>
     </row>
     <row r="832">
@@ -15493,7 +15493,7 @@
         <v>12</v>
       </c>
       <c r="D841">
-        <v>0.000972289742343</v>
+        <v>0.0009722897423430002</v>
       </c>
     </row>
     <row r="842">
@@ -17851,7 +17851,7 @@
         <v>12</v>
       </c>
       <c r="D972">
-        <v>0.000972289742343</v>
+        <v>0.0009722897423430002</v>
       </c>
     </row>
     <row r="973">
@@ -18265,7 +18265,7 @@
         <v>12</v>
       </c>
       <c r="D995">
-        <v>0.000972289742343</v>
+        <v>0.0009722897423430002</v>
       </c>
     </row>
     <row r="996">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1080">
@@ -21757,7 +21757,7 @@
         <v>113</v>
       </c>
       <c r="D1189">
-        <v>0.009155728407065</v>
+        <v>0.009155728407065002</v>
       </c>
     </row>
     <row r="1190">
@@ -22254,7 +22254,7 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1217">
